--- a/alt-tests/TC_Result.xlsx
+++ b/alt-tests/TC_Result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\funity\Test1\alt-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D293813-88A3-4D9E-84B9-FD529C903AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EEABF9-5503-4D67-B44C-B2CDD210F95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="1965" windowWidth="34530" windowHeight="18525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1575" yWindow="1965" windowWidth="33285" windowHeight="18525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="113">
   <si>
     <t>ID</t>
   </si>
@@ -348,13 +348,28 @@
     <t>test_tc_mj_009_pipeline_failure_sample</t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>20260519_162356</t>
   </si>
   <si>
     <t>20260519_162447</t>
+  </si>
+  <si>
+    <t>20260520_091653</t>
+  </si>
+  <si>
+    <t>20260520_091801</t>
+  </si>
+  <si>
+    <t>20260521_132419</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>20260521_132517</t>
+  </si>
+  <si>
+    <t>20260521_132626</t>
   </si>
 </sst>
 </file>
@@ -651,11 +666,11 @@
     <xf numFmtId="22" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1058,7 +1073,7 @@
         <v>77</v>
       </c>
       <c r="I2" s="18">
-        <v>46161.683900462966</v>
+        <v>46163.560046296298</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1087,7 +1102,7 @@
         <v>77</v>
       </c>
       <c r="I3" s="18">
-        <v>46161.683935185189</v>
+        <v>46163.560081018521</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1116,7 +1131,7 @@
         <v>77</v>
       </c>
       <c r="I4" s="18">
-        <v>46161.683969907404</v>
+        <v>46163.560115740744</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1145,7 +1160,7 @@
         <v>77</v>
       </c>
       <c r="I5" s="18">
-        <v>46161.684016203704</v>
+        <v>46163.560150462959</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1174,7 +1189,7 @@
         <v>77</v>
       </c>
       <c r="I6" s="18">
-        <v>46161.684050925927</v>
+        <v>46163.560185185182</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1203,7 +1218,7 @@
         <v>77</v>
       </c>
       <c r="I7" s="18">
-        <v>46161.684074074074</v>
+        <v>46163.560208333336</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1232,7 +1247,7 @@
         <v>77</v>
       </c>
       <c r="I8" s="18">
-        <v>46161.68408564815</v>
+        <v>46163.560231481482</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1261,7 +1276,7 @@
         <v>77</v>
       </c>
       <c r="I9" s="18">
-        <v>46161.684120370373</v>
+        <v>46163.560254629629</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1290,7 +1305,7 @@
         <v>103</v>
       </c>
       <c r="I10" s="21">
-        <v>46161.684131944443</v>
+        <v>46163.558796296296</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1304,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.875" style="1" bestFit="1" customWidth="1"/>
@@ -3343,7 +3358,7 @@
       <c r="E82" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="F82" s="25" t="s">
+      <c r="F82" s="24" t="s">
         <v>103</v>
       </c>
       <c r="G82" s="23">
@@ -3352,7 +3367,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B83" s="12">
         <v>46161.683287037034</v>
@@ -3375,7 +3390,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B84" s="12">
         <v>46161.683287037034</v>
@@ -3398,7 +3413,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B85" s="12">
         <v>46161.683287037034</v>
@@ -3421,7 +3436,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B86" s="12">
         <v>46161.683287037034</v>
@@ -3444,7 +3459,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B87" s="12">
         <v>46161.683287037034</v>
@@ -3467,7 +3482,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B88" s="12">
         <v>46161.683287037034</v>
@@ -3490,7 +3505,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B89" s="12">
         <v>46161.683287037034</v>
@@ -3513,7 +3528,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B90" s="12">
         <v>46161.683287037034</v>
@@ -3536,7 +3551,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B91" s="12">
         <v>46161.683877314812</v>
@@ -3559,7 +3574,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B92" s="12">
         <v>46161.683877314812</v>
@@ -3582,7 +3597,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B93" s="12">
         <v>46161.683877314812</v>
@@ -3605,7 +3620,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B94" s="12">
         <v>46161.683877314812</v>
@@ -3628,7 +3643,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B95" s="12">
         <v>46161.683877314812</v>
@@ -3651,7 +3666,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B96" s="12">
         <v>46161.683877314812</v>
@@ -3674,7 +3689,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B97" s="12">
         <v>46161.683877314812</v>
@@ -3697,7 +3712,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B98" s="12">
         <v>46161.683877314812</v>
@@ -3720,7 +3735,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B99" s="23">
         <v>46161.683877314812</v>
@@ -3739,6 +3754,972 @@
       </c>
       <c r="G99" s="23">
         <v>46161.684131944443</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="12">
+        <v>46162.386724537035</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="12">
+        <v>46162.386747685188</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="12">
+        <v>46162.386724537035</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E101" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="12">
+        <v>46162.386782407404</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" s="12">
+        <v>46162.386724537035</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" s="12">
+        <v>46162.386828703704</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B103" s="12">
+        <v>46162.386724537035</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" s="12">
+        <v>46162.386863425927</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104" s="12">
+        <v>46162.386724537035</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E104" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G104" s="12">
+        <v>46162.38689814815</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B105" s="12">
+        <v>46162.386724537035</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E105" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G105" s="12">
+        <v>46162.386921296296</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" s="12">
+        <v>46162.386724537035</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E106" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" s="12">
+        <v>46162.386956018519</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" s="12">
+        <v>46162.386724537035</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E107" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" s="12">
+        <v>46162.386979166666</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B108" s="12">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E108" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G108" s="12">
+        <v>46162.38753472222</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B109" s="12">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E109" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" s="12">
+        <v>46162.387569444443</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B110" s="12">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" s="12">
+        <v>46162.387604166666</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B111" s="12">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E111" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" s="12">
+        <v>46162.387650462966</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B112" s="12">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G112" s="12">
+        <v>46162.387685185182</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B113" s="12">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" s="12">
+        <v>46162.387708333335</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B114" s="12">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" s="12">
+        <v>46162.387731481482</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B115" s="12">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" s="12">
+        <v>46162.387754629628</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B116" s="23">
+        <v>46162.387511574074</v>
+      </c>
+      <c r="C116" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D116" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E116" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F116" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="G116" s="23">
+        <v>46162.387766203705</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B117" s="12">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E117" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F117" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" s="12">
+        <v>46163.558576388888</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B118" s="12">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" s="12">
+        <v>46163.558611111112</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B119" s="12">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" s="12">
+        <v>46163.558645833335</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B120" s="12">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" s="12">
+        <v>46163.558680555558</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B121" s="12">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E121" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" s="12">
+        <v>46163.558715277781</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B122" s="12">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F122" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" s="12">
+        <v>46163.558738425927</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B123" s="12">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E123" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G123" s="12">
+        <v>46163.558761574073</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B124" s="12">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E124" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="12">
+        <v>46163.55878472222</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B125" s="23">
+        <v>46163.558553240742</v>
+      </c>
+      <c r="C125" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D125" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E125" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F125" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="G125" s="23">
+        <v>46163.558796296296</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B126" s="12">
+        <v>46163.559224537035</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E126" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="12">
+        <v>46163.559247685182</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B127" s="12">
+        <v>46163.559224537035</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E127" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" s="12">
+        <v>46163.559282407405</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B128" s="12">
+        <v>46163.559224537035</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" s="12">
+        <v>46163.559317129628</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B129" s="12">
+        <v>46163.559224537035</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E129" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" s="12">
+        <v>46163.559351851851</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B130" s="12">
+        <v>46163.559224537035</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E130" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G130" s="12">
+        <v>46163.559386574074</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B131" s="12">
+        <v>46163.559224537035</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E131" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G131" s="12">
+        <v>46163.55940972222</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B132" s="12">
+        <v>46163.559224537035</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E132" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F132" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G132" s="12">
+        <v>46163.559421296297</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B133" s="12">
+        <v>46163.559224537035</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G133" s="12">
+        <v>46163.55945601852</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B134" s="12">
+        <v>46163.560023148151</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E134" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F134" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G134" s="12">
+        <v>46163.560046296298</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B135" s="12">
+        <v>46163.560023148151</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E135" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G135" s="12">
+        <v>46163.560081018521</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B136" s="12">
+        <v>46163.560023148151</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E136" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F136" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G136" s="12">
+        <v>46163.560115740744</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B137" s="12">
+        <v>46163.560023148151</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E137" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F137" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G137" s="12">
+        <v>46163.560150462959</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B138" s="12">
+        <v>46163.560023148151</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E138" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F138" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G138" s="12">
+        <v>46163.560185185182</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B139" s="12">
+        <v>46163.560023148151</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E139" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F139" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G139" s="12">
+        <v>46163.560208333336</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B140" s="12">
+        <v>46163.560023148151</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E140" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G140" s="12">
+        <v>46163.560231481482</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B141" s="12">
+        <v>46163.560023148151</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E141" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" s="12">
+        <v>46163.560254629629</v>
       </c>
     </row>
   </sheetData>
@@ -3769,7 +4750,7 @@
         <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -3777,7 +4758,7 @@
         <v>83</v>
       </c>
       <c r="B3" s="13">
-        <v>46161.683877314812</v>
+        <v>46163.560023148151</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3785,7 +4766,7 @@
         <v>84</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3801,7 +4782,7 @@
         <v>86</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -3825,15 +4806,15 @@
         <v>89</v>
       </c>
       <c r="B9" s="14">
-        <v>0.88890000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>105</v>
+      <c r="B10" s="25" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
